--- a/РАБОЧИЙ СТОЛ/машины Останкино СЫРЫ.xlsx
+++ b/РАБОЧИЙ СТОЛ/машины Останкино СЫРЫ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39ADA67D-2930-4638-AD6D-7AF14BD40BF3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FAA23E8-AB81-4817-B51E-D3B32E4ECB7E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>Доброцен-Донецк</t>
   </si>
@@ -88,6 +88,9 @@
   </si>
   <si>
     <t>4 машина</t>
+  </si>
+  <si>
+    <t>Мариуполь</t>
   </si>
 </sst>
 </file>
@@ -529,7 +532,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
@@ -585,7 +588,7 @@
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
       <c r="G3" s="2">
-        <f t="shared" ref="G3:G11" si="0">B3-C3-D3-E3-F3</f>
+        <f t="shared" ref="G3:G12" si="0">B3-C3-D3-E3-F3</f>
         <v>0</v>
       </c>
     </row>
@@ -661,7 +664,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -675,7 +678,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -689,7 +692,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -701,65 +704,79 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="4">
-        <f t="shared" ref="B12:G12" si="1">SUM(B2:B11)</f>
-        <v>0</v>
-      </c>
-      <c r="C12" s="4">
+      <c r="B13" s="4">
+        <f t="shared" ref="B13:G13" si="1">SUM(B2:B12)</f>
+        <v>0</v>
+      </c>
+      <c r="C13" s="4">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="D12" s="4">
+      <c r="D13" s="4">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="E12" s="4">
+      <c r="E13" s="4">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F12" s="4">
+      <c r="F13" s="4">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G12" s="4">
+      <c r="G13" s="4">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="14" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C14" s="6" t="s">
+    <row r="14" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="15" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C15" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D14" s="7"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="9"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C15" s="3">
-        <f>IF(ROUNDUP(C12/500,0)&gt;32,32,ROUNDUP(C12/500,0))</f>
-        <v>0</v>
-      </c>
-      <c r="D15" s="3">
-        <f t="shared" ref="D15:F15" si="2">IF(ROUNDUP(D12/500,0)&gt;32,32,ROUNDUP(D12/500,0))</f>
-        <v>0</v>
-      </c>
-      <c r="E15" s="3">
-        <f t="shared" ref="E15" si="3">IF(ROUNDUP(E12/500,0)&gt;32,32,ROUNDUP(E12/500,0))</f>
-        <v>0</v>
-      </c>
-      <c r="F15" s="3">
+      <c r="D15" s="7"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="9"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C16" s="3">
+        <f>IF(ROUNDUP(C13/500,0)&gt;32,32,ROUNDUP(C13/500,0))</f>
+        <v>0</v>
+      </c>
+      <c r="D16" s="3">
+        <f t="shared" ref="D16:F16" si="2">IF(ROUNDUP(D13/500,0)&gt;32,32,ROUNDUP(D13/500,0))</f>
+        <v>0</v>
+      </c>
+      <c r="E16" s="3">
+        <f t="shared" ref="E16" si="3">IF(ROUNDUP(E13/500,0)&gt;32,32,ROUNDUP(E13/500,0))</f>
+        <v>0</v>
+      </c>
+      <c r="F16" s="3">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="C15:F15"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/РАБОЧИЙ СТОЛ/машины Останкино СЫРЫ.xlsx
+++ b/РАБОЧИЙ СТОЛ/машины Останкино СЫРЫ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FAA23E8-AB81-4817-B51E-D3B32E4ECB7E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{633519DC-B31F-4374-B449-930014679E90}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="22">
   <si>
     <t>Доброцен-Донецк</t>
   </si>
@@ -91,6 +91,12 @@
   </si>
   <si>
     <t>Мариуполь</t>
+  </si>
+  <si>
+    <t>с Крымом</t>
+  </si>
+  <si>
+    <t>5 машина</t>
   </si>
 </sst>
 </file>
@@ -135,7 +141,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -159,19 +165,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -208,19 +201,6 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
       <top style="medium">
         <color indexed="64"/>
       </top>
@@ -233,25 +213,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -532,39 +505,43 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="6" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.85546875" customWidth="1"/>
+    <col min="8" max="8" width="8.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -573,12 +550,13 @@
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
-      <c r="G2" s="2">
+      <c r="G2" s="2"/>
+      <c r="H2" s="2">
         <f>B2-C2-D2-E2-F2</f>
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -587,12 +565,13 @@
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
-      <c r="G3" s="2">
-        <f t="shared" ref="G3:G12" si="0">B3-C3-D3-E3-F3</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G3" s="2"/>
+      <c r="H3" s="2">
+        <f t="shared" ref="H3:H12" si="0">B3-C3-D3-E3-F3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
@@ -601,12 +580,13 @@
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
-      <c r="G4" s="2">
+      <c r="G4" s="2"/>
+      <c r="H4" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>17</v>
       </c>
@@ -615,12 +595,13 @@
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
-      <c r="G5" s="2">
+      <c r="G5" s="2"/>
+      <c r="H5" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>1</v>
       </c>
@@ -629,12 +610,16 @@
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
-      <c r="G6" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G6" s="2"/>
+      <c r="H6" s="2">
+        <f>B6-C6-D6-E6-F6-G6</f>
+        <v>0</v>
+      </c>
+      <c r="I6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>2</v>
       </c>
@@ -643,12 +628,13 @@
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
-      <c r="G7" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G7" s="2"/>
+      <c r="H7" s="2">
+        <f t="shared" ref="H7:H10" si="1">B7-C7-D7-E7-F7-G7</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>3</v>
       </c>
@@ -657,12 +643,13 @@
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
-      <c r="G8" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G8" s="2"/>
+      <c r="H8" s="2">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>19</v>
       </c>
@@ -671,12 +658,16 @@
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
-      <c r="G9" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G9" s="2"/>
+      <c r="H9" s="2">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>4</v>
       </c>
@@ -685,12 +676,16 @@
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
-      <c r="G10" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G10" s="2"/>
+      <c r="H10" s="2">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>8</v>
       </c>
@@ -699,12 +694,13 @@
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
-      <c r="G11" s="2">
+      <c r="G11" s="2"/>
+      <c r="H11" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>7</v>
       </c>
@@ -713,70 +709,79 @@
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
-      <c r="G12" s="2">
+      <c r="G12" s="2"/>
+      <c r="H12" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
+    <row r="13" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="4">
-        <f t="shared" ref="B13:G13" si="1">SUM(B2:B12)</f>
-        <v>0</v>
-      </c>
-      <c r="C13" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="D13" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E13" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F13" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G13" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="15" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C15" s="6" t="s">
+      <c r="B13" s="3">
+        <f t="shared" ref="B13:H13" si="2">SUM(B2:B12)</f>
+        <v>0</v>
+      </c>
+      <c r="C13" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D13" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E13" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F13" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G13" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H13" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C15" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D15" s="7"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="9"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C16" s="3">
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+    </row>
+    <row r="16" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C16" s="6">
         <f>IF(ROUNDUP(C13/500,0)&gt;32,32,ROUNDUP(C13/500,0))</f>
         <v>0</v>
       </c>
-      <c r="D16" s="3">
-        <f t="shared" ref="D16:F16" si="2">IF(ROUNDUP(D13/500,0)&gt;32,32,ROUNDUP(D13/500,0))</f>
-        <v>0</v>
-      </c>
-      <c r="E16" s="3">
-        <f t="shared" ref="E16" si="3">IF(ROUNDUP(E13/500,0)&gt;32,32,ROUNDUP(E13/500,0))</f>
-        <v>0</v>
-      </c>
-      <c r="F16" s="3">
-        <f t="shared" si="2"/>
+      <c r="D16" s="7">
+        <f t="shared" ref="D16:G16" si="3">IF(ROUNDUP(D13/500,0)&gt;32,32,ROUNDUP(D13/500,0))</f>
+        <v>0</v>
+      </c>
+      <c r="E16" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F16" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="G16" s="8">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="C15:G15"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/РАБОЧИЙ СТОЛ/машины Останкино СЫРЫ.xlsx
+++ b/РАБОЧИЙ СТОЛ/машины Останкино СЫРЫ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{633519DC-B31F-4374-B449-930014679E90}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36C84D54-CA86-4777-BFBE-B2E942BED187}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="21">
   <si>
     <t>Доброцен-Донецк</t>
   </si>
@@ -66,15 +66,6 @@
     <t>ОБЩИИЙ ВЕС</t>
   </si>
   <si>
-    <t>1 машина</t>
-  </si>
-  <si>
-    <t>2 машина</t>
-  </si>
-  <si>
-    <t>3 машина</t>
-  </si>
-  <si>
     <t>Остаток</t>
   </si>
   <si>
@@ -87,16 +78,22 @@
     <t>Малахутин</t>
   </si>
   <si>
-    <t>4 машина</t>
-  </si>
-  <si>
     <t>Мариуполь</t>
   </si>
   <si>
     <t>с Крымом</t>
   </si>
   <si>
-    <t>5 машина</t>
+    <t>осн.заказ</t>
+  </si>
+  <si>
+    <t>предзаказ</t>
+  </si>
+  <si>
+    <t>сети</t>
+  </si>
+  <si>
+    <t>масло</t>
   </si>
 </sst>
 </file>
@@ -141,7 +138,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -184,21 +181,6 @@
         <color indexed="64"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
         <color indexed="64"/>
       </right>
       <top style="medium">
@@ -219,12 +201,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -505,17 +489,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="6" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.85546875" customWidth="1"/>
-    <col min="8" max="8" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>9</v>
       </c>
@@ -523,25 +506,19 @@
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -549,14 +526,12 @@
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2">
-        <f>B2-C2-D2-E2-F2</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F2" s="2" t="e">
+        <f>B2-C2-D2-#REF!-#REF!</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -564,14 +539,12 @@
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2">
-        <f t="shared" ref="H3:H12" si="0">B3-C3-D3-E3-F3</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F3" s="2" t="e">
+        <f>B3-C3-D3-#REF!-#REF!</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
@@ -579,113 +552,131 @@
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F4" s="2" t="e">
+        <f>B4-C4-D4-#REF!-#REF!</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F5" s="2" t="e">
+        <f>B5-C5-D5-#REF!-#REF!</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
+      <c r="B6" s="2">
+        <v>2768</v>
+      </c>
+      <c r="C6" s="2">
+        <v>2426</v>
+      </c>
+      <c r="D6" s="2">
+        <v>342</v>
+      </c>
       <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2">
-        <f>B6-C6-D6-E6-F6-G6</f>
-        <v>0</v>
-      </c>
-      <c r="I6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F6" s="2">
+        <f>B6-C6-D6-E6</f>
+        <v>0</v>
+      </c>
+      <c r="G6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2">
-        <f t="shared" ref="H7:H10" si="1">B7-C7-D7-E7-F7-G7</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B7" s="2">
+        <v>1057</v>
+      </c>
+      <c r="C7" s="2">
+        <v>541</v>
+      </c>
+      <c r="D7" s="2">
+        <v>126</v>
+      </c>
+      <c r="E7" s="2">
+        <v>390</v>
+      </c>
+      <c r="F7" s="2">
+        <f t="shared" ref="F7:F13" si="0">B7-C7-D7-E7</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
+      <c r="B8" s="2">
+        <v>572</v>
+      </c>
+      <c r="C8" s="2">
+        <v>554</v>
+      </c>
+      <c r="D8" s="2">
+        <v>18</v>
+      </c>
       <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F8" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
+        <v>15</v>
+      </c>
+      <c r="B9" s="2">
+        <v>478</v>
+      </c>
+      <c r="C9" s="2">
+        <v>455</v>
+      </c>
+      <c r="D9" s="2">
+        <v>23</v>
+      </c>
       <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I9" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F9" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
+      <c r="B10" s="2">
+        <v>1545</v>
+      </c>
+      <c r="C10" s="2">
+        <v>915</v>
+      </c>
+      <c r="D10" s="2">
+        <v>630</v>
+      </c>
       <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I10" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F10" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>8</v>
       </c>
@@ -693,14 +684,12 @@
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2">
+      <c r="F11" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>7</v>
       </c>
@@ -708,80 +697,65 @@
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2">
+      <c r="F12" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B13" s="3">
-        <f t="shared" ref="B13:H13" si="2">SUM(B2:B12)</f>
-        <v>0</v>
+        <f t="shared" ref="B13:D13" si="1">SUM(B2:B12)</f>
+        <v>6420</v>
       </c>
       <c r="C13" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>4891</v>
       </c>
       <c r="D13" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>1139</v>
       </c>
       <c r="E13" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F13" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G13" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H13" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C15" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-    </row>
-    <row r="16" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C16" s="6">
+        <f t="shared" ref="E13" si="2">SUM(E2:E12)</f>
+        <v>390</v>
+      </c>
+      <c r="F13" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D14" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C15" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D15" s="8"/>
+      <c r="E15" s="7"/>
+    </row>
+    <row r="16" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C16" s="5">
         <f>IF(ROUNDUP(C13/500,0)&gt;32,32,ROUNDUP(C13/500,0))</f>
-        <v>0</v>
-      </c>
-      <c r="D16" s="7">
-        <f t="shared" ref="D16:G16" si="3">IF(ROUNDUP(D13/500,0)&gt;32,32,ROUNDUP(D13/500,0))</f>
-        <v>0</v>
-      </c>
-      <c r="E16" s="7">
+        <v>10</v>
+      </c>
+      <c r="D16" s="6">
+        <f t="shared" ref="D16:E16" si="3">IF(ROUNDUP(D13/500,0)&gt;32,32,ROUNDUP(D13/500,0))</f>
+        <v>3</v>
+      </c>
+      <c r="E16" s="6">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="F16" s="7">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="G16" s="8">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="C15:D15"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
